--- a/incident_report_forms/006_use_of_force_assessment_form--incident_report_forms.xlsx
+++ b/incident_report_forms/006_use_of_force_assessment_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -800,8 +800,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,12 +829,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane_smith',_'label':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Smith', 'label': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'jim_brown',_'label':_'jim_brown'}</t>
+          <t>jim_brown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Jim Brown', 'label': 'Jim Brown'}</t>
+          <t>Jim Brown</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'suspect_1',_'label':_'suspect_1'}</t>
+          <t>suspect_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Suspect 1', 'label': 'Suspect 1'}</t>
+          <t>Suspect 1</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'suspect_2',_'label':_'suspect_2'}</t>
+          <t>suspect_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Suspect 2', 'label': 'Suspect 2'}</t>
+          <t>Suspect 2</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'suspect_3',_'label':_'suspect_3'}</t>
+          <t>suspect_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Suspect 3', 'label': 'Suspect 3'}</t>
+          <t>Suspect 3</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'witness_1',_'label':_'witness_1'}</t>
+          <t>witness_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 1', 'label': 'Witness 1'}</t>
+          <t>Witness 1</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'witness_2',_'label':_'witness_2'}</t>
+          <t>witness_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 2', 'label': 'Witness 2'}</t>
+          <t>Witness 2</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'witness_3',_'label':_'witness_3'}</t>
+          <t>witness_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 3', 'label': 'Witness 3'}</t>
+          <t>Witness 3</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'officer_1',_'label':_'officer_1'}</t>
+          <t>officer_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Officer 1', 'label': 'Officer 1'}</t>
+          <t>Officer 1</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'officer_2',_'label':_'officer_2'}</t>
+          <t>officer_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Officer 2', 'label': 'Officer 2'}</t>
+          <t>Officer 2</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'officer_3',_'label':_'officer_3'}</t>
+          <t>officer_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Officer 3', 'label': 'Officer 3'}</t>
+          <t>Officer 3</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'response_1',_'label':_'response_1'}</t>
+          <t>response_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Response 1', 'label': 'Response 1'}</t>
+          <t>Response 1</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'response_2',_'label':_'response_2'}</t>
+          <t>response_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Response 2', 'label': 'Response 2'}</t>
+          <t>Response 2</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'response_3',_'label':_'response_3'}</t>
+          <t>response_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Response 3', 'label': 'Response 3'}</t>
+          <t>Response 3</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'open',_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Open', 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'closed',_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Closed', 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
